--- a/testdata/realdata/splice_boxes.xlsx
+++ b/testdata/realdata/splice_boxes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -447,6 +447,11 @@
           <t>经纬度</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>状态</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -479,6 +484,11 @@
           <t>126.62762,45.75936</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -511,6 +521,11 @@
           <t>125.8145,46.02637</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -543,6 +558,11 @@
           <t>125.8145,46.02637</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -575,6 +595,11 @@
           <t>125.32856,46.41143</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,6 +632,11 @@
           <t>125.32856,46.41143</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -639,6 +669,11 @@
           <t>125.10148,46.5969</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -671,6 +706,11 @@
           <t>125.10148,46.5969</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -703,6 +743,11 @@
           <t>123.94954,47.33924</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -735,6 +780,11 @@
           <t>126.62762,45.75936</t>
         </is>
       </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -767,6 +817,11 @@
           <t>127.1604,45.47508</t>
         </is>
       </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -799,6 +854,11 @@
           <t>127.1604,45.47508</t>
         </is>
       </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -831,6 +891,11 @@
           <t>128.31581,44.9802</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -863,6 +928,11 @@
           <t>128.31581,44.9802</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -895,6 +965,11 @@
           <t>129.61138,44.57902</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -927,6 +1002,11 @@
           <t>126.62762,45.75936</t>
         </is>
       </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -959,6 +1039,11 @@
           <t>127.46029,45.74342</t>
         </is>
       </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -991,6 +1076,11 @@
           <t>127.46029,45.74342</t>
         </is>
       </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1023,6 +1113,11 @@
           <t>128.92725,45.78637</t>
         </is>
       </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1055,6 +1150,11 @@
           <t>128.92725,45.78637</t>
         </is>
       </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1087,6 +1187,11 @@
           <t>129.56504,46.32081</t>
         </is>
       </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1119,6 +1224,11 @@
           <t>129.56504,46.32081</t>
         </is>
       </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1151,6 +1261,11 @@
           <t>130.37472,46.80374</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1183,6 +1298,11 @@
           <t>130.37472,46.80374</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1215,6 +1335,11 @@
           <t>130.55706,46.23543</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1247,6 +1372,11 @@
           <t>130.55706,46.23543</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1279,6 +1409,11 @@
           <t>131.00666,45.77036</t>
         </is>
       </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1311,6 +1446,11 @@
           <t>131.00666,45.77036</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1343,6 +1483,11 @@
           <t>130.96193,45.29285</t>
         </is>
       </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1375,6 +1520,11 @@
           <t>130.96193,45.29285</t>
         </is>
       </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1407,6 +1557,11 @@
           <t>129.61138,44.57902</t>
         </is>
       </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1439,6 +1594,11 @@
           <t>123.94954,47.33924</t>
         </is>
       </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1471,6 +1631,11 @@
           <t>125.11985,48.45402</t>
         </is>
       </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1503,6 +1668,11 @@
           <t>125.11985,48.45402</t>
         </is>
       </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1535,6 +1705,11 @@
           <t>125.23123,49.17348</t>
         </is>
       </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1567,6 +1742,11 @@
           <t>125.23123,49.17348</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1599,6 +1779,11 @@
           <t>124.13165,50.40579</t>
         </is>
       </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1631,6 +1816,11 @@
           <t>124.13165,50.40579</t>
         </is>
       </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1663,6 +1853,11 @@
           <t>124.70199,52.33318</t>
         </is>
       </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1695,6 +1890,11 @@
           <t>124.70199,52.33318</t>
         </is>
       </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1727,6 +1927,11 @@
           <t>122.533,52.97144</t>
         </is>
       </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1759,6 +1964,11 @@
           <t>126.62762,45.75936</t>
         </is>
       </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1791,6 +2001,11 @@
           <t>126.96272,46.65104</t>
         </is>
       </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1823,6 +2038,11 @@
           <t>126.96272,46.65104</t>
         </is>
       </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1855,6 +2075,11 @@
           <t>128.5499,46.8564</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1887,6 +2112,11 @@
           <t>128.5499,46.8564</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>在网</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1917,6 +2147,11 @@
       <c r="F47" t="inlineStr">
         <is>
           <t>128.83376,47.72537</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>在网</t>
         </is>
       </c>
     </row>
